--- a/tests/workbooktests/workbooks/test_scheduler.xlsx
+++ b/tests/workbooktests/workbooks/test_scheduler.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA935D6-D010-4EAE-A2AE-D05F03BF5B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9449E-2F56-4455-9B59-241A5C77459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{3B901BD3-1520-4A7D-BDDE-23C97D5E1476}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{3B901BD3-1520-4A7D-BDDE-23C97D5E1476}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -235,10 +235,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -264,12 +271,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CC1430-2ADC-46A4-ABD8-44E39011F1C0}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -741,9 +749,9 @@
       <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="str" cm="1">
-        <f t="array" ref="C13">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R13C3Schedule,A</v>
+      <c r="C13" t="e" cm="1">
+        <f t="array" aca="1" ref="C13" ca="1">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -753,532 +761,407 @@
       <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" t="str" cm="1">
-        <f t="array" ref="C14">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9,C10)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R14C3Schedule,A</v>
+      <c r="C14" t="e" cm="1">
+        <f t="array" aca="1" ref="C14" ca="1">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9,C10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="C15" t="str" cm="1">
-        <f t="array" ref="C15">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9,,C11)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R15C3Schedule,A</v>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlSchedule(C2,C3,C4,C5,C6,C7,C8,C9,,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="str" cm="1">
-        <f t="array" ref="C16">_xll.qlScheduleFromDates(_xlfn.ANCHORARRAY(C31))</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R16C3Schedule,A</v>
+      <c r="C16" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">_xll.qlScheduleFromDates(_xlfn.ANCHORARRAY(C31))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="2" cm="1">
-        <f t="array" ref="C18:C22">_xll.qlScheduleDates(C13)</f>
-        <v>45799</v>
+      <c r="C18" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlScheduleDates(C13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C19" s="2">
-        <v>45891</v>
-      </c>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C20" s="2">
-        <v>45985</v>
-      </c>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C21" s="2">
-        <v>46076</v>
-      </c>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C22" s="2">
-        <v>46164</v>
-      </c>
+      <c r="C22" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="2" cm="1">
-        <f t="array" ref="C24:C29">_xll.qlScheduleDates(C14)</f>
-        <v>45799</v>
+      <c r="C24" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlScheduleDates(C14)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C25" s="2">
-        <v>45807</v>
-      </c>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C26" s="2">
-        <v>45891</v>
-      </c>
+      <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C27" s="2">
-        <v>45985</v>
-      </c>
+      <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C28" s="2">
-        <v>46076</v>
-      </c>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C29" s="2">
-        <v>46164</v>
-      </c>
+      <c r="C29" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="2" cm="1">
-        <f t="array" ref="C31:C35">_xll.qlScheduleDates(C15)</f>
-        <v>45799</v>
+      <c r="C31" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C31" ca="1">_xll.qlScheduleDates(C15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C32" s="2">
-        <v>45880</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C33" s="2">
-        <v>45971</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C34" s="2">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C35" s="2">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C35" s="2"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="2" cm="1">
-        <f t="array" ref="C37:C41">_xll.qlScheduleDates(C16)</f>
-        <v>45799</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C38" s="2">
-        <v>45880</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C39" s="2">
-        <v>45971</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C40" s="2">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C41" s="2">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C37" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C37" ca="1">_xll.qlScheduleDates(C16)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C41" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="2" cm="1">
-        <f t="array" ref="C44">_xll.qlSchedulePreviousDate(C13,C19)</f>
-        <v>45799</v>
-      </c>
-      <c r="D44" s="2" cm="1">
-        <f t="array" ref="D44">_xll.qlSchedulePreviousDate(C16,C38)</f>
-        <v>45799</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C44" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C44" ca="1">_xll.qlSchedulePreviousDate(C13,C19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D44" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D44" ca="1">_xll.qlSchedulePreviousDate(C16,C38)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="2" cm="1">
-        <f t="array" ref="C45">_xll.qlScheduleNextDate(C13,C22)</f>
-        <v>46164</v>
-      </c>
-      <c r="D45" s="2" cm="1">
-        <f t="array" ref="D45">_xll.qlScheduleNextDate(C16,C40)</f>
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C45" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C45" ca="1">_xll.qlScheduleNextDate(C13,C22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D45" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D45" ca="1">_xll.qlScheduleNextDate(C16,C40)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>36</v>
       </c>
-      <c r="C46" t="b" cm="1">
-        <f t="array" ref="C46">_xll.qlScheduleHasIsRegular(C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D46" t="b" cm="1">
-        <f t="array" ref="D46">_xll.qlScheduleHasIsRegular(C16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C46" t="e" cm="1">
+        <f t="array" aca="1" ref="C46" ca="1">_xll.qlScheduleHasIsRegular(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D46" t="e" cm="1">
+        <f t="array" aca="1" ref="D46" ca="1">_xll.qlScheduleHasIsRegular(C16)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="b" cm="1">
-        <f t="array" ref="C47">_xll.qlScheduleIsRegular(C13,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D47" t="str" cm="1">
-        <f t="array" ref="D47">_xll.qlScheduleIsRegular(C16,1)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: full interface (isRegular) not available
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 152, in qlScheduleIsRegular
-    return schedule.isRegular(i)
-           ~~~~~~~~~~~~~~~~~~^^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 11132, in isRegular
-    return _QuantLib.Schedule_isRegular(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: full interface (isRegular) not available
-</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C47" t="e" cm="1">
+        <f t="array" aca="1" ref="C47" ca="1">_xll.qlScheduleIsRegular(C13,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D47" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="D47" ca="1">FIND("RuntimeError: RuntimeError: full interface", _xll.qlScheduleIsRegular(C16,1))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>52</v>
       </c>
-      <c r="C48" t="b" cm="1">
-        <f t="array" ref="C48:F48">TRANSPOSE(_xll.qlScheduleIsRegular2(C13))</f>
-        <v>1</v>
-      </c>
-      <c r="D48" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" t="b">
-        <v>1</v>
+      <c r="C48" t="e" cm="1">
+        <f t="array" aca="1" ref="C48" ca="1">TRANSPOSE(_xll.qlScheduleIsRegular2(C13))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>37</v>
       </c>
-      <c r="C49" t="str" cm="1">
-        <f t="array" ref="C49">_xll.qlScheduleCalendar(C13)</f>
-        <v>TARGET</v>
-      </c>
-      <c r="D49" t="str" cm="1">
-        <f t="array" ref="D49">_xll.qlScheduleCalendar(C16)</f>
-        <v>Null</v>
+      <c r="C49" t="e" cm="1">
+        <f t="array" aca="1" ref="C49" ca="1">_xll.qlScheduleCalendar(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D49" t="e" cm="1">
+        <f t="array" aca="1" ref="D49" ca="1">_xll.qlScheduleCalendar(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="2" cm="1">
-        <f t="array" ref="C50">_xll.qlScheduleStartDate(C13)</f>
-        <v>45799</v>
-      </c>
-      <c r="D50" s="2" cm="1">
-        <f t="array" ref="D50">_xll.qlScheduleStartDate(C16)</f>
-        <v>45799</v>
+      <c r="C50" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C50" ca="1">_xll.qlScheduleStartDate(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D50" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D50" ca="1">_xll.qlScheduleStartDate(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="2" cm="1">
-        <f t="array" ref="C51">_xll.qlScheduleEndDate(C13)</f>
-        <v>46164</v>
-      </c>
-      <c r="D51" s="2" cm="1">
-        <f t="array" ref="D51">_xll.qlScheduleEndDate(C16)</f>
-        <v>46164</v>
+      <c r="C51" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C51" ca="1">_xll.qlScheduleEndDate(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D51" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D51" ca="1">_xll.qlScheduleEndDate(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="C52" t="b" cm="1">
-        <f t="array" ref="C52">_xll.qlScheduleHasTenor(C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D52" t="b" cm="1">
-        <f t="array" ref="D52">_xll.qlScheduleHasTenor(C16)</f>
-        <v>0</v>
+      <c r="C52" t="e" cm="1">
+        <f t="array" aca="1" ref="C52" ca="1">_xll.qlScheduleHasTenor(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D52" t="e" cm="1">
+        <f t="array" aca="1" ref="D52" ca="1">_xll.qlScheduleHasTenor(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="C53" t="str" cm="1">
-        <f t="array" ref="C53">_xll.qlScheduleTenor(C13)</f>
-        <v>3M</v>
-      </c>
-      <c r="D53" t="str" cm="1">
-        <f t="array" ref="D53">_xll.qlScheduleTenor(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: full interface (tenor) not available
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 218, in qlScheduleTenor
-    return schedule.tenor()
-           ~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 11152, in tenor
-    return _QuantLib.Schedule_tenor(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: full interface (tenor) not available
-</v>
+      <c r="C53" t="e" cm="1">
+        <f t="array" aca="1" ref="C53" ca="1">_xll.qlScheduleTenor(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D53" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="D53" ca="1">FIND("RuntimeError: RuntimeError: full interface", _xll.qlScheduleTenor(C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>41</v>
       </c>
-      <c r="C54" t="str" cm="1">
-        <f t="array" ref="C54">_xll.qlScheduleBusinessDayConvention(C13)</f>
-        <v xml:space="preserve">NameError: NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 229, in qlScheduleBusinessDayConvention
-    return first_key(QL_BUSINESSDAYCONVENTION, schedule.businessDayConvention(), UNKNOWN_VALUE)
-                     ^^^^^^^^^^^^^^^^^^^^^^^^
-NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-</v>
-      </c>
-      <c r="D54" t="str" cm="1">
-        <f t="array" ref="D54">_xll.qlScheduleBusinessDayConvention(C16)</f>
-        <v xml:space="preserve">NameError: NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 229, in qlScheduleBusinessDayConvention
-    return first_key(QL_BUSINESSDAYCONVENTION, schedule.businessDayConvention(), UNKNOWN_VALUE)
-                     ^^^^^^^^^^^^^^^^^^^^^^^^
-NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-</v>
+      <c r="C54" t="e" cm="1">
+        <f t="array" aca="1" ref="C54" ca="1">_xll.qlScheduleBusinessDayConvention(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D54" t="e" cm="1">
+        <f t="array" aca="1" ref="D54" ca="1">_xll.qlScheduleBusinessDayConvention(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>42</v>
       </c>
-      <c r="C55" t="b" cm="1">
-        <f t="array" ref="C55">_xll.qlScheduleHasTerminationDateBusinessDayConvention(C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D55" t="b" cm="1">
-        <f t="array" ref="D55">_xll.qlScheduleHasTerminationDateBusinessDayConvention(C16)</f>
-        <v>0</v>
+      <c r="C55" t="e" cm="1">
+        <f t="array" aca="1" ref="C55" ca="1">_xll.qlScheduleHasTerminationDateBusinessDayConvention(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D55" t="e" cm="1">
+        <f t="array" aca="1" ref="D55" ca="1">_xll.qlScheduleHasTerminationDateBusinessDayConvention(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>43</v>
       </c>
-      <c r="C56" t="str" cm="1">
-        <f t="array" ref="C56">_xll.qlScheduleTerminationDateBusinessDayConvention(C13)</f>
-        <v xml:space="preserve">NameError: NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 251, in qlScheduleTerminationDateBusinessDayConvention
-    return first_key(QL_BUSINESSDAYCONVENTION, schedule.terminationDateBusinessDayConvention(), UNKNOWN_VALUE)
-                     ^^^^^^^^^^^^^^^^^^^^^^^^
-NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-</v>
-      </c>
-      <c r="D56" t="str" cm="1">
-        <f t="array" ref="D56">_xll.qlScheduleTerminationDateBusinessDayConvention(C16)</f>
-        <v xml:space="preserve">NameError: NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 251, in qlScheduleTerminationDateBusinessDayConvention
-    return first_key(QL_BUSINESSDAYCONVENTION, schedule.terminationDateBusinessDayConvention(), UNKNOWN_VALUE)
-                     ^^^^^^^^^^^^^^^^^^^^^^^^
-NameError: name 'QL_BUSINESSDAYCONVENTION' is not defined
-</v>
+      <c r="C56" t="e" cm="1">
+        <f t="array" aca="1" ref="C56" ca="1">_xll.qlScheduleTerminationDateBusinessDayConvention(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D56" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="D56" ca="1">FIND("RuntimeError: RuntimeError: full interface", _xll.qlScheduleTerminationDateBusinessDayConvention(C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>44</v>
       </c>
-      <c r="C57" t="b" cm="1">
-        <f t="array" ref="C57">_xll.qlScheduleHasRule(C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D57" t="b" cm="1">
-        <f t="array" ref="D57">_xll.qlScheduleHasRule(C16)</f>
-        <v>0</v>
+      <c r="C57" t="e" cm="1">
+        <f t="array" aca="1" ref="C57" ca="1">_xll.qlScheduleHasRule(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D57" t="e" cm="1">
+        <f t="array" aca="1" ref="D57" ca="1">_xll.qlScheduleHasRule(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>45</v>
       </c>
-      <c r="C58" t="str" cm="1">
-        <f t="array" ref="C58">_xll.qlScheduleRule(C13)</f>
-        <v>BACKWARD</v>
-      </c>
-      <c r="D58" t="str" cm="1">
-        <f t="array" ref="D58">_xll.qlScheduleRule(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: full interface (rule) not available
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 273, in qlScheduleRule
-    return first_key(QL_DATEGENERATION_RULE, schedule.rule(), UNKNOWN_VALUE)
-                                             ~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 11172, in rule
-    return _QuantLib.Schedule_rule(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: full interface (rule) not available
-</v>
+      <c r="C58" t="e" cm="1">
+        <f t="array" aca="1" ref="C58" ca="1">_xll.qlScheduleRule(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D58" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="D58" ca="1">FIND("RuntimeError: RuntimeError: full interface",_xll.qlScheduleRule(C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>46</v>
       </c>
-      <c r="C59" t="b" cm="1">
-        <f t="array" ref="C59">_xll.qlScheduleHasEndOfMonth(C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D59" t="b" cm="1">
-        <f t="array" ref="D59">_xll.qlScheduleHasEndOfMonth(C16)</f>
-        <v>0</v>
+      <c r="C59" t="e" cm="1">
+        <f t="array" aca="1" ref="C59" ca="1">_xll.qlScheduleHasEndOfMonth(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D59" t="e" cm="1">
+        <f t="array" aca="1" ref="D59" ca="1">_xll.qlScheduleHasEndOfMonth(C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>47</v>
       </c>
-      <c r="C60" t="b" cm="1">
-        <f t="array" ref="C60">_xll.qlScheduleEndOfMonth(C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" t="str" cm="1">
-        <f t="array" ref="D60">_xll.qlScheduleEndOfMonth(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: full interface (end of month) not available
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\scheduler.py", line 295, in qlScheduleEndOfMonth
-    return schedule.endOfMonth()
-           ~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 11180, in endOfMonth
-    return _QuantLib.Schedule_endOfMonth(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: full interface (end of month) not available
-</v>
+      <c r="C60" t="e" cm="1">
+        <f t="array" aca="1" ref="C60" ca="1">_xll.qlScheduleEndOfMonth(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D60" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="D60" ca="1">FIND("RuntimeError: RuntimeError: full interface",_xll.qlScheduleEndOfMonth(C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>48</v>
       </c>
-      <c r="C61" t="str" cm="1">
-        <f t="array" ref="C61">_xll.qlScheduleAfter(C13,C19)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R61C3Schedule,A</v>
-      </c>
-      <c r="D61" t="str" cm="1">
-        <f t="array" ref="D61">_xll.qlScheduleAfter(C16,C38)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R61C4Schedule,A</v>
+      <c r="C61" t="e" cm="1">
+        <f t="array" aca="1" ref="C61" ca="1">_xll.qlScheduleAfter(C13,C19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D61" t="e" cm="1">
+        <f t="array" aca="1" ref="D61" ca="1">_xll.qlScheduleAfter(C16,C38)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>49</v>
       </c>
-      <c r="C62" t="str" cm="1">
-        <f t="array" ref="C62">_xll.qlScheduleUntil(C13,C21)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R62C3Schedule,A</v>
-      </c>
-      <c r="D62" t="str" cm="1">
-        <f t="array" ref="D62">_xll.qlScheduleUntil(C16,C39)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R62C4Schedule,A</v>
+      <c r="C62" t="e" cm="1">
+        <f t="array" aca="1" ref="C62" ca="1">_xll.qlScheduleUntil(C13,C21)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D62" t="e" cm="1">
+        <f t="array" aca="1" ref="D62" ca="1">_xll.qlScheduleUntil(C16,C39)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>30</v>
       </c>
-      <c r="C64" s="2" cm="1">
-        <f t="array" ref="C64:C67">_xll.qlScheduleDates(C61)</f>
-        <v>45891</v>
-      </c>
-      <c r="D64" s="2" cm="1">
-        <f t="array" ref="D64:D67">_xll.qlScheduleDates(D61)</f>
-        <v>45880</v>
+      <c r="C64" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C64" ca="1">_xll.qlScheduleDates(C61)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D64" ca="1">_xll.qlScheduleDates(D61)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C65" s="2">
-        <v>45985</v>
-      </c>
-      <c r="D65" s="2">
-        <v>45971</v>
-      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C66" s="2">
-        <v>46076</v>
-      </c>
-      <c r="D66" s="2">
-        <v>46063</v>
-      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C67" s="2">
-        <v>46164</v>
-      </c>
-      <c r="D67" s="2">
-        <v>46164</v>
-      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>30</v>
       </c>
-      <c r="C69" s="2" cm="1">
-        <f t="array" ref="C69:C72">_xll.qlScheduleDates(C62)</f>
-        <v>45799</v>
-      </c>
-      <c r="D69" s="2" cm="1">
-        <f t="array" ref="D69:D71">_xll.qlScheduleDates(D62)</f>
-        <v>45799</v>
+      <c r="C69" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C69" ca="1">_xll.qlScheduleDates(C62)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D69" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D69" ca="1">_xll.qlScheduleDates(D62)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C70" s="2">
-        <v>45891</v>
-      </c>
-      <c r="D70" s="2">
-        <v>45880</v>
-      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C71" s="2">
-        <v>45985</v>
-      </c>
-      <c r="D71" s="2">
-        <v>45971</v>
-      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C72" s="2">
-        <v>46076</v>
-      </c>
+      <c r="C72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C73" s="2"/>
@@ -1295,29 +1178,25 @@
       <c r="A75" t="s">
         <v>53</v>
       </c>
-      <c r="C75" t="str" cm="1">
-        <f t="array" ref="C75">_xll.qlMakeSchedule(C2,C3,,C74)</f>
-        <v>欣[test_scheduler.xlsx]Schedule!R75C3Schedule,A</v>
+      <c r="C75" t="e" cm="1">
+        <f t="array" aca="1" ref="C75" ca="1">_xll.qlMakeSchedule(C2,C3,,C74)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>30</v>
       </c>
-      <c r="C76" s="2" cm="1">
-        <f t="array" ref="C76:C78">_xll.qlScheduleDates(C75)</f>
-        <v>45799</v>
+      <c r="C76" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C76" ca="1">_xll.qlScheduleDates(C75)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C77" s="2">
-        <v>45983</v>
-      </c>
+      <c r="C77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C78" s="2">
-        <v>46164</v>
-      </c>
+      <c r="C78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C79" s="2"/>
